--- a/data/trans_orig/P68-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P68-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93459</t>
+          <t>93924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130473</t>
+          <t>130014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126679</t>
+          <t>126307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170500</t>
+          <t>169820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244514</t>
+          <t>244973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281528</t>
+          <t>281063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100530</t>
+          <t>99943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122478</t>
+          <t>123198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355499</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>399320</t>
+          <t>399692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256348</t>
+          <t>255359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>317390</t>
+          <t>316321</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99273</t>
+          <t>99337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>136723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372115</t>
+          <t>373136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>444361</t>
+          <t>442629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>795748</t>
+          <t>796817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>856790</t>
+          <t>857779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441727</t>
+          <t>442371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479821</t>
+          <t>479757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1247871</t>
+          <t>1249603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1320117</t>
+          <t>1319096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58813</t>
+          <t>59683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>90633</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50428</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77642</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118198</t>
+          <t>117316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160952</t>
+          <t>160206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313904</t>
+          <t>314677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346497</t>
+          <t>345627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213716</t>
+          <t>212415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>239861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535716</t>
+          <t>536462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578470</t>
+          <t>579352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>432161</t>
+          <t>434510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>506905</t>
+          <t>510003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195809</t>
+          <t>196389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249326</t>
+          <t>247541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>644460</t>
+          <t>646055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>737682</t>
+          <t>740870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1386530</t>
+          <t>1383432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1461274</t>
+          <t>1458925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>772138</t>
+          <t>773923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>825655</t>
+          <t>825075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2177217</t>
+          <t>2174029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2270439</t>
+          <t>2268844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46888</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71808</t>
+          <t>71693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>27454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81620</t>
+          <t>81889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>114424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112210</t>
+          <t>112325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137130</t>
+          <t>138293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>90878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>112523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209979</t>
+          <t>209571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242375</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199464</t>
+          <t>200203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253625</t>
+          <t>254018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109534</t>
+          <t>113078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152898</t>
+          <t>152235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>323724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393650</t>
+          <t>392025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>660900</t>
+          <t>660507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>715061</t>
+          <t>714322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419975</t>
+          <t>420638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463339</t>
+          <t>459795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1093747</t>
+          <t>1095372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1163583</t>
+          <t>1163673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>34215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62165</t>
+          <t>61015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>34207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61551</t>
+          <t>60274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75940</t>
+          <t>74707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111890</t>
+          <t>111718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>254092</t>
+          <t>255242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281155</t>
+          <t>282042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173346</t>
+          <t>174623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199849</t>
+          <t>200690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439264</t>
+          <t>439436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475214</t>
+          <t>476447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298788</t>
+          <t>298910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>364414</t>
+          <t>363615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190408</t>
+          <t>191311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>244374</t>
+          <t>247103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>506362</t>
+          <t>510530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>584174</t>
+          <t>591191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1050386</t>
+          <t>1051185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1116012</t>
+          <t>1115890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>703373</t>
+          <t>700644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757339</t>
+          <t>756436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1778373</t>
+          <t>1771356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856185</t>
+          <t>1852017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>44353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60507</t>
+          <t>59771</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>87669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>71890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96648</t>
+          <t>95614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59479</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>123339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150501</t>
+          <t>151237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203217</t>
+          <t>204028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258605</t>
+          <t>257110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106142</t>
+          <t>103232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146971</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320981</t>
+          <t>319342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>387906</t>
+          <t>389475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661752</t>
+          <t>663247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>717140</t>
+          <t>716329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504807</t>
+          <t>506111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>545636</t>
+          <t>548546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1184229</t>
+          <t>1182660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1251154</t>
+          <t>1252793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49580</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81250</t>
+          <t>81458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>60180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90901</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116997</t>
+          <t>114460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159817</t>
+          <t>158635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265364</t>
+          <t>265156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297034</t>
+          <t>297406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214477</t>
+          <t>215123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246280</t>
+          <t>245198</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>492175</t>
+          <t>493357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>534995</t>
+          <t>537532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>315904</t>
+          <t>316405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>380945</t>
+          <t>382777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189712</t>
+          <t>190735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243154</t>
+          <t>241835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>524749</t>
+          <t>526318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>607799</t>
+          <t>609260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1025994</t>
+          <t>1024162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1091035</t>
+          <t>1090534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>785043</t>
+          <t>786362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>838485</t>
+          <t>837462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1827337</t>
+          <t>1825876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910387</t>
+          <t>1908818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69932</t>
+          <t>68713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91309</t>
+          <t>92166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111856</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>41766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>62629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>143999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170978</t>
+          <t>171340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124391</t>
+          <t>141429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>302963</t>
+          <t>303579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188260</t>
+          <t>184549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>309597</t>
+          <t>316947</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>345202</t>
+          <t>337741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576223</t>
+          <t>566409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1056491</t>
+          <t>1055875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1235063</t>
+          <t>1218025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>618649</t>
+          <t>611299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>739986</t>
+          <t>743697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1711477</t>
+          <t>1721291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1942498</t>
+          <t>1949959</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52685</t>
+          <t>55365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88487</t>
+          <t>89487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76477</t>
+          <t>74494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107190</t>
+          <t>105518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138766</t>
+          <t>139340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184340</t>
+          <t>183807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>356965</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>392767</t>
+          <t>390087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329124</t>
+          <t>330796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359837</t>
+          <t>361820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>697426</t>
+          <t>697959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743000</t>
+          <t>742426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220703</t>
+          <t>220888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>399871</t>
+          <t>404307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303903</t>
+          <t>300676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>434415</t>
+          <t>434694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>557443</t>
+          <t>529111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>785016</t>
+          <t>790612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1537137</t>
+          <t>1532701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1716305</t>
+          <t>1716120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010755</t>
+          <t>1010476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1141267</t>
+          <t>1144494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2597162</t>
+          <t>2591566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2824735</t>
+          <t>2853067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P68-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P68-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93924</t>
+          <t>94423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130014</t>
+          <t>131113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>49489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>128107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169820</t>
+          <t>170282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244973</t>
+          <t>243874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281063</t>
+          <t>280564</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99943</t>
+          <t>101523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123198</t>
+          <t>122911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356179</t>
+          <t>355717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>399692</t>
+          <t>397892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>255359</t>
+          <t>256680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>316321</t>
+          <t>319534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99337</t>
+          <t>99878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136723</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373136</t>
+          <t>372967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442629</t>
+          <t>442836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>796817</t>
+          <t>793604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>857779</t>
+          <t>856458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442371</t>
+          <t>442598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479757</t>
+          <t>479216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1249603</t>
+          <t>1249396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1319096</t>
+          <t>1319265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>58425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90633</t>
+          <t>91018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51497</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>78471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117316</t>
+          <t>118321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160206</t>
+          <t>159068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314677</t>
+          <t>314292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>345627</t>
+          <t>346885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212415</t>
+          <t>212887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239861</t>
+          <t>241011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>536462</t>
+          <t>537600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579352</t>
+          <t>578347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>434510</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>510003</t>
+          <t>508849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>190991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247541</t>
+          <t>247029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646055</t>
+          <t>648329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>740870</t>
+          <t>738299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1383432</t>
+          <t>1384586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1458925</t>
+          <t>1463337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>773923</t>
+          <t>774435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>825075</t>
+          <t>830473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2174029</t>
+          <t>2176600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2268844</t>
+          <t>2266570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71693</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>50045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81889</t>
+          <t>80163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114424</t>
+          <t>114480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>112730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138293</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90878</t>
+          <t>89932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112523</t>
+          <t>111184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209571</t>
+          <t>209515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>243832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200203</t>
+          <t>199382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254018</t>
+          <t>254359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113078</t>
+          <t>109732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152235</t>
+          <t>152218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323724</t>
+          <t>323461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392025</t>
+          <t>392367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>660507</t>
+          <t>660166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>714322</t>
+          <t>715143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>420638</t>
+          <t>420655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459795</t>
+          <t>463141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1095372</t>
+          <t>1095030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1163673</t>
+          <t>1163936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34215</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61015</t>
+          <t>59332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34207</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60274</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74707</t>
+          <t>75883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111718</t>
+          <t>113079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255242</t>
+          <t>256925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>282572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174623</t>
+          <t>173083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200690</t>
+          <t>199461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439436</t>
+          <t>438075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476447</t>
+          <t>475271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298910</t>
+          <t>298747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>363615</t>
+          <t>365684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191311</t>
+          <t>190493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247103</t>
+          <t>243195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>510530</t>
+          <t>507201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>591191</t>
+          <t>588626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1051185</t>
+          <t>1049116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1115890</t>
+          <t>1116053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700644</t>
+          <t>704552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>756436</t>
+          <t>757254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1771356</t>
+          <t>1773921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1852017</t>
+          <t>1855346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44353</t>
+          <t>43834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68077</t>
+          <t>67517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59771</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87669</t>
+          <t>87608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71890</t>
+          <t>72450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95614</t>
+          <t>96133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44641</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123339</t>
+          <t>123400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151237</t>
+          <t>151624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204028</t>
+          <t>202211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257110</t>
+          <t>254782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103232</t>
+          <t>106647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145667</t>
+          <t>148124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>325058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>389475</t>
+          <t>385244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>663247</t>
+          <t>665575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>716329</t>
+          <t>718146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506111</t>
+          <t>503654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>548546</t>
+          <t>545131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1182660</t>
+          <t>1186891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252793</t>
+          <t>1247077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49208</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81458</t>
+          <t>79962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60180</t>
+          <t>58461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114460</t>
+          <t>116125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158635</t>
+          <t>161608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265156</t>
+          <t>266652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297406</t>
+          <t>297760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215123</t>
+          <t>216426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245198</t>
+          <t>246917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>493357</t>
+          <t>490384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>537532</t>
+          <t>535867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316405</t>
+          <t>315597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>382777</t>
+          <t>382128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190735</t>
+          <t>191925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241835</t>
+          <t>244831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526318</t>
+          <t>520687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609260</t>
+          <t>606464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1024162</t>
+          <t>1024811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1090534</t>
+          <t>1091342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>786362</t>
+          <t>783366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>837462</t>
+          <t>836272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1825876</t>
+          <t>1828672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1908818</t>
+          <t>1914449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>48331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54200</t>
+          <t>60722</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41372</t>
+          <t>48202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68713</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102889</t>
+          <t>127719</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92166</t>
+          <t>115604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111573</t>
+          <t>137655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55623</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41766</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>71222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>158512</t>
+          <t>191813</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143999</t>
+          <t>176503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171340</t>
+          <t>204333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>239580</t>
+          <t>269736</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141429</t>
+          <t>237501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303579</t>
+          <t>299304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>238368</t>
+          <t>220862</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184549</t>
+          <t>196969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316947</t>
+          <t>243475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>477948</t>
+          <t>490598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>337741</t>
+          <t>452245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>566409</t>
+          <t>535161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1119874</t>
+          <t>980147</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1055875</t>
+          <t>950579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1218025</t>
+          <t>1012382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>689878</t>
+          <t>704996</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>611299</t>
+          <t>682383</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>743697</t>
+          <t>728889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1809752</t>
+          <t>1685143</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1721291</t>
+          <t>1640580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1949959</t>
+          <t>1723496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1359454</t>
+          <t>1249883</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1359454</t>
+          <t>1249883</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1359454</t>
+          <t>1249883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>928246</t>
+          <t>925858</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>928246</t>
+          <t>925858</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>928246</t>
+          <t>925858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2287700</t>
+          <t>2175741</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2287700</t>
+          <t>2175741</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2287700</t>
+          <t>2175741</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69526</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89487</t>
+          <t>99876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74494</t>
+          <t>84244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105518</t>
+          <t>115279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>160221</t>
+          <t>177175</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139340</t>
+          <t>153869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183807</t>
+          <t>202719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>375926</t>
+          <t>407934</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>355965</t>
+          <t>385822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390087</t>
+          <t>425247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>345619</t>
+          <t>379928</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330796</t>
+          <t>364060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361820</t>
+          <t>395095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>721545</t>
+          <t>787862</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>697959</t>
+          <t>762318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>742426</t>
+          <t>811168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,06%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>445452</t>
+          <t>485698</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>445452</t>
+          <t>485698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>445452</t>
+          <t>485698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>479339</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>479339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>479339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>881766</t>
+          <t>965037</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>881766</t>
+          <t>965037</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>881766</t>
+          <t>965037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>338320</t>
+          <t>383716</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220888</t>
+          <t>345634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>404307</t>
+          <t>423244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>354049</t>
+          <t>344779</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>300676</t>
+          <t>317788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>434694</t>
+          <t>371579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>692369</t>
+          <t>728496</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>529111</t>
+          <t>679247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>790612</t>
+          <t>776903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1598688</t>
+          <t>1515799</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1532701</t>
+          <t>1476271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1716120</t>
+          <t>1553881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1091121</t>
+          <t>1149018</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010476</t>
+          <t>1122218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1144494</t>
+          <t>1176009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2689809</t>
+          <t>2664816</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2591566</t>
+          <t>2616409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2853067</t>
+          <t>2714065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1937008</t>
+          <t>1899515</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1937008</t>
+          <t>1899515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1937008</t>
+          <t>1899515</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1445170</t>
+          <t>1493797</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1445170</t>
+          <t>1493797</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1445170</t>
+          <t>1493797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3382178</t>
+          <t>3393312</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3382178</t>
+          <t>3393312</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3382178</t>
+          <t>3393312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P68-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
